--- a/signup_forms/035_customer_sign_up_quote_request--signup_forms.xlsx
+++ b/signup_forms/035_customer_sign_up_quote_request--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Type Options</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Status Options</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Quote Terms</t>
+          <t>Quote Terms Terms</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quote_terms_terms</t>
+          <t>quote_terms_terms_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quote Terms</t>
+          <t>Quote Terms Terms 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>quote_terms_terms_2</t>
+          <t>quote_terms_terms_2_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quote Terms</t>
+          <t>Quote Terms Terms 2 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_sign_up</t>
+          <t>customer_sign_up_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Sign Up</t>
+          <t>Customer Sign Up 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
